--- a/data/trans_dic/P25C$productsfarma_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,7</t>
+          <t>0,0; 39,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,47</t>
+          <t>0,0; 26,98</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,76</t>
+          <t>0,0; 55,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>0,0; 24,29</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,37</t>
+          <t>0,0; 22,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,54</t>
+          <t>1,24; 10,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 13,24</t>
+          <t>2,03; 12,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,44</t>
+          <t>0,95; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,41</t>
+          <t>0,13; 4,1</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,26</t>
+          <t>2,99; 10,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,1</t>
+          <t>0,56; 5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,22</t>
+          <t>2,53; 7,25</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,79</t>
+          <t>0,84; 4,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,37</t>
+          <t>0,94; 4,56</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,23</t>
+          <t>0,0; 14,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,39</t>
+          <t>0,3; 4,08</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,73</t>
+          <t>0,97; 4,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,38</t>
+          <t>1,81; 5,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,16</t>
+          <t>1,45; 4,16</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7264</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8170</t>
+          <t>0; 7005</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11312</t>
+          <t>0; 11394</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 12830</t>
+          <t>0; 12434</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10058</t>
+          <t>0; 10250</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>652; 5500</t>
+          <t>646; 5662</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1925; 12862</t>
+          <t>1969; 12223</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 17587</t>
+          <t>0; 18018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>762; 6478</t>
+          <t>830; 6568</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>778; 19128</t>
+          <t>559; 17801</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4389; 16101</t>
+          <t>4684; 15807</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>499; 5261</t>
+          <t>485; 4641</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5953; 17542</t>
+          <t>6161; 17617</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1191; 7445</t>
+          <t>1310; 7681</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3263</t>
+          <t>0; 3598</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1919; 8780</t>
+          <t>1885; 9166</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4573</t>
+          <t>0; 4469</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3046</t>
+          <t>0; 2641</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>408; 4551</t>
+          <t>408; 5483</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8387; 40205</t>
+          <t>8218; 38177</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5844; 18144</t>
+          <t>6096; 16891</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15660; 49324</t>
+          <t>17238; 49429</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$productsfarma_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,37</t>
+          <t>0,0; 37,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>0,0; 37,84</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,16</t>
+          <t>0,0; 48,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,29</t>
+          <t>0,0; 22,54</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,79</t>
+          <t>0,0; 25,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,85</t>
+          <t>1,14; 10,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,58</t>
+          <t>1,93; 14,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,81; 8,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,54</t>
+          <t>1,49; 8,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,1</t>
+          <t>1,55; 6,97</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,08</t>
+          <t>2,57; 8,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,38</t>
+          <t>0,55; 5,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,25</t>
+          <t>2,39; 7,02</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,94</t>
+          <t>0,77; 4,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,56</t>
+          <t>0,96; 4,6</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,94</t>
+          <t>0,0; 14,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,08</t>
+          <t>0,29; 3,93</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,49</t>
+          <t>2,33; 5,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,01</t>
+          <t>1,76; 5,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,16</t>
+          <t>2,49; 4,97</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1691</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 7598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7005</t>
+          <t>0; 10121</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4176</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11394</t>
+          <t>0; 12480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 12434</t>
+          <t>0; 13477</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5944</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10250</t>
+          <t>0; 12729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646; 5662</t>
+          <t>645; 5861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1969; 12223</t>
+          <t>2037; 15840</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6901</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 18018</t>
+          <t>916; 9430</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>830; 6568</t>
+          <t>1379; 7735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>559; 17801</t>
+          <t>3187; 14359</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10553</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4684; 15807</t>
+          <t>4236; 14679</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>485; 4641</t>
+          <t>523; 5365</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6161; 17617</t>
+          <t>6210; 18223</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4886</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1310; 7681</t>
+          <t>1329; 8165</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3598</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1885; 9166</t>
+          <t>2112; 10135</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>908</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1777</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4469</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2641</t>
+          <t>0; 2780</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>408; 5483</t>
+          <t>430; 5823</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8218; 38177</t>
+          <t>15407; 36890</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6096; 16891</t>
+          <t>6448; 18308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17238; 49429</t>
+          <t>25587; 50963</t>
         </is>
       </c>
     </row>
